--- a/meta-insights.xlsx
+++ b/meta-insights.xlsx
@@ -3,7 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Meta Insights" sheetId="1" r:id="rId1"/>
+    <sheet name="All Campaigns" sheetId="1" r:id="rId1"/>
+    <sheet name="Best Campaigns" sheetId="2" r:id="rId2"/>
+    <sheet name="Worst Campaigns" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
@@ -397,379 +399,845 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:I16"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>campaign_name</v>
+        <v>campaignId</v>
       </c>
       <c r="B1" t="str">
+        <v>campaignName</v>
+      </c>
+      <c r="C1" t="str">
         <v>spend</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>clicks</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
+        <v>impressions</v>
+      </c>
+      <c r="F1" t="str">
         <v>ctr</v>
       </c>
-      <c r="E1" t="str">
+      <c r="G1" t="str">
         <v>cpm</v>
       </c>
-      <c r="F1" t="str">
-        <v>date_start</v>
-      </c>
-      <c r="G1" t="str">
-        <v>date_stop</v>
+      <c r="H1" t="str">
+        <v>roas</v>
+      </c>
+      <c r="I1" t="str">
+        <v>score</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
+        <v>120213783804790425</v>
+      </c>
+      <c r="B2" t="str">
         <v>FB/PR/Advantage+</v>
       </c>
-      <c r="B2" t="str">
-        <v>19529.76</v>
-      </c>
-      <c r="C2" t="str">
-        <v>2879</v>
-      </c>
-      <c r="D2" t="str">
-        <v>2.24389</v>
-      </c>
-      <c r="E2" t="str">
-        <v>152.21474</v>
-      </c>
-      <c r="F2" t="str">
-        <v>2026-05-11</v>
-      </c>
-      <c r="G2" t="str">
-        <v>2026-05-17</v>
+      <c r="C2">
+        <v>29827.38</v>
+      </c>
+      <c r="D2">
+        <v>4869</v>
+      </c>
+      <c r="E2">
+        <v>234847</v>
+      </c>
+      <c r="F2">
+        <v>2.073265</v>
+      </c>
+      <c r="G2">
+        <v>127.007711</v>
+      </c>
+      <c r="H2">
+        <v>5.239972</v>
+      </c>
+      <c r="I2">
+        <v>290.7631289</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
+        <v>120213798531480425</v>
+      </c>
+      <c r="B3" t="str">
         <v>FB/RT</v>
       </c>
-      <c r="B3" t="str">
-        <v>44984.14</v>
-      </c>
-      <c r="C3" t="str">
-        <v>7102</v>
-      </c>
-      <c r="D3" t="str">
-        <v>1.72801</v>
-      </c>
-      <c r="E3" t="str">
-        <v>109.452326</v>
-      </c>
-      <c r="F3" t="str">
-        <v>2026-05-11</v>
-      </c>
-      <c r="G3" t="str">
-        <v>2026-05-17</v>
+      <c r="C3">
+        <v>34879.94</v>
+      </c>
+      <c r="D3">
+        <v>5978</v>
+      </c>
+      <c r="E3">
+        <v>333807</v>
+      </c>
+      <c r="F3">
+        <v>1.790855</v>
+      </c>
+      <c r="G3">
+        <v>104.491338</v>
+      </c>
+      <c r="H3">
+        <v>5.619023</v>
+      </c>
+      <c r="I3">
+        <v>306.3191162</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
+        <v>120214021839830425</v>
+      </c>
+      <c r="B4" t="str">
         <v>FB/RT/İçerik</v>
       </c>
-      <c r="B4" t="str">
-        <v>14148.62</v>
-      </c>
-      <c r="C4" t="str">
-        <v>2532</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2.01104</v>
-      </c>
-      <c r="E4" t="str">
-        <v>112.375362</v>
-      </c>
-      <c r="F4" t="str">
-        <v>2026-05-11</v>
-      </c>
-      <c r="G4" t="str">
-        <v>2026-05-17</v>
+      <c r="C4">
+        <v>13348.16</v>
+      </c>
+      <c r="D4">
+        <v>2354</v>
+      </c>
+      <c r="E4">
+        <v>112476</v>
+      </c>
+      <c r="F4">
+        <v>2.092891</v>
+      </c>
+      <c r="G4">
+        <v>118.675629</v>
+      </c>
+      <c r="H4">
+        <v>5.55955</v>
+      </c>
+      <c r="I4">
+        <v>307.9677571</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
+        <v>120229177507470425</v>
+      </c>
+      <c r="B5" t="str">
         <v>FB/RT/Dynamic</v>
       </c>
-      <c r="B5" t="str">
-        <v>5471.21</v>
-      </c>
-      <c r="C5" t="str">
-        <v>899</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2.130837</v>
-      </c>
-      <c r="E5" t="str">
-        <v>129.680256</v>
-      </c>
-      <c r="F5" t="str">
-        <v>2026-05-11</v>
-      </c>
-      <c r="G5" t="str">
-        <v>2026-05-17</v>
+      <c r="C5">
+        <v>4846.68</v>
+      </c>
+      <c r="D5">
+        <v>877</v>
+      </c>
+      <c r="E5">
+        <v>38990</v>
+      </c>
+      <c r="F5">
+        <v>2.249295</v>
+      </c>
+      <c r="G5">
+        <v>124.305719</v>
+      </c>
+      <c r="H5">
+        <v>8.248112</v>
+      </c>
+      <c r="I5">
+        <v>444.96092810000005</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
+        <v>120229338955800425</v>
+      </c>
+      <c r="B6" t="str">
         <v>FB/RT/Crousel</v>
       </c>
-      <c r="B6" t="str">
-        <v>2728.57</v>
-      </c>
-      <c r="C6" t="str">
-        <v>623</v>
-      </c>
-      <c r="D6" t="str">
-        <v>1.824465</v>
-      </c>
-      <c r="E6" t="str">
-        <v>79.90658</v>
-      </c>
-      <c r="F6" t="str">
-        <v>2026-05-11</v>
-      </c>
-      <c r="G6" t="str">
-        <v>2026-05-17</v>
+      <c r="C6">
+        <v>2003.7</v>
+      </c>
+      <c r="D6">
+        <v>463</v>
+      </c>
+      <c r="E6">
+        <v>24075</v>
+      </c>
+      <c r="F6">
+        <v>1.923157</v>
+      </c>
+      <c r="G6">
+        <v>83.227414</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>30.140398600000005</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
+        <v>120230011729980425</v>
+      </c>
+      <c r="B7" t="str">
         <v>FB/PR/İlgi Alanı</v>
       </c>
-      <c r="B7" t="str">
-        <v>17766.4</v>
-      </c>
-      <c r="C7" t="str">
-        <v>3004</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2.448248</v>
-      </c>
-      <c r="E7" t="str">
-        <v>144.795436</v>
-      </c>
-      <c r="F7" t="str">
-        <v>2026-05-11</v>
-      </c>
-      <c r="G7" t="str">
-        <v>2026-05-17</v>
+      <c r="C7">
+        <v>12388.98</v>
+      </c>
+      <c r="D7">
+        <v>2132</v>
+      </c>
+      <c r="E7">
+        <v>84969</v>
+      </c>
+      <c r="F7">
+        <v>2.50915</v>
+      </c>
+      <c r="G7">
+        <v>145.805882</v>
+      </c>
+      <c r="H7">
+        <v>2.577604</v>
+      </c>
+      <c r="I7">
+        <v>164.4826118</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
+        <v>120238452559310425</v>
+      </c>
+      <c r="B8" t="str">
         <v>FB/RT/Traffik/Mağaza</v>
       </c>
-      <c r="B8" t="str">
-        <v>1879.79</v>
-      </c>
-      <c r="C8" t="str">
-        <v>666</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2.023886</v>
-      </c>
-      <c r="E8" t="str">
-        <v>57.12432</v>
-      </c>
-      <c r="F8" t="str">
-        <v>2026-05-11</v>
-      </c>
-      <c r="G8" t="str">
-        <v>2026-05-17</v>
+      <c r="C8">
+        <v>1387.19</v>
+      </c>
+      <c r="D8">
+        <v>457</v>
+      </c>
+      <c r="E8">
+        <v>24613</v>
+      </c>
+      <c r="F8">
+        <v>1.856742</v>
+      </c>
+      <c r="G8">
+        <v>56.360054</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>31.498834599999995</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
+        <v>120245580624510425</v>
+      </c>
+      <c r="B9" t="str">
         <v>Satışlar-DENEME SEVDE</v>
       </c>
-      <c r="B9" t="str">
-        <v>1904.71</v>
-      </c>
-      <c r="C9" t="str">
-        <v>2540</v>
-      </c>
-      <c r="D9" t="str">
-        <v>3.923568</v>
-      </c>
-      <c r="E9" t="str">
-        <v>29.422278</v>
-      </c>
-      <c r="F9" t="str">
-        <v>2026-05-11</v>
-      </c>
-      <c r="G9" t="str">
-        <v>2026-05-17</v>
+      <c r="C9">
+        <v>1413.83</v>
+      </c>
+      <c r="D9">
+        <v>1841</v>
+      </c>
+      <c r="E9">
+        <v>46537</v>
+      </c>
+      <c r="F9">
+        <v>3.955992</v>
+      </c>
+      <c r="G9">
+        <v>30.380772</v>
+      </c>
+      <c r="H9">
+        <v>0.551693</v>
+      </c>
+      <c r="I9">
+        <v>103.6664128</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
+        <v>120245818053700425</v>
+      </c>
+      <c r="B10" t="str">
         <v>Reels - Bayram İndirimi  - Test</v>
       </c>
-      <c r="B10" t="str">
-        <v>759.76</v>
-      </c>
-      <c r="C10" t="str">
-        <v>131</v>
-      </c>
-      <c r="D10" t="str">
-        <v>2.045597</v>
-      </c>
-      <c r="E10" t="str">
-        <v>118.638351</v>
-      </c>
-      <c r="F10" t="str">
-        <v>2026-05-11</v>
-      </c>
-      <c r="G10" t="str">
-        <v>2026-05-17</v>
+      <c r="C10">
+        <v>475.9</v>
+      </c>
+      <c r="D10">
+        <v>74</v>
+      </c>
+      <c r="E10">
+        <v>3890</v>
+      </c>
+      <c r="F10">
+        <v>1.902314</v>
+      </c>
+      <c r="G10">
+        <v>122.339332</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>25.8123468</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
+        <v>120245821039980425</v>
+      </c>
+      <c r="B11" t="str">
         <v>Reels - Takım - Test</v>
       </c>
-      <c r="B11" t="str">
-        <v>1697.8</v>
-      </c>
-      <c r="C11" t="str">
-        <v>453</v>
-      </c>
-      <c r="D11" t="str">
-        <v>2.62487</v>
-      </c>
-      <c r="E11" t="str">
-        <v>98.377564</v>
-      </c>
-      <c r="F11" t="str">
-        <v>2026-05-11</v>
-      </c>
-      <c r="G11" t="str">
-        <v>2026-05-17</v>
+      <c r="C11">
+        <v>1685</v>
+      </c>
+      <c r="D11">
+        <v>455</v>
+      </c>
+      <c r="E11">
+        <v>16933</v>
+      </c>
+      <c r="F11">
+        <v>2.687061</v>
+      </c>
+      <c r="G11">
+        <v>99.509833</v>
+      </c>
+      <c r="H11">
+        <v>7.64505</v>
+      </c>
+      <c r="I11">
+        <v>426.0427367</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
+        <v>120245821072940425</v>
+      </c>
+      <c r="B12" t="str">
         <v>Çok Satanlar Kategorisi - Carousel - Test</v>
       </c>
-      <c r="B12" t="str">
-        <v>761.55</v>
-      </c>
-      <c r="C12" t="str">
-        <v>115</v>
-      </c>
-      <c r="D12" t="str">
-        <v>1.943224</v>
-      </c>
-      <c r="E12" t="str">
-        <v>128.683677</v>
-      </c>
-      <c r="F12" t="str">
-        <v>2026-05-11</v>
-      </c>
-      <c r="G12" t="str">
-        <v>2026-05-17</v>
+      <c r="C12">
+        <v>489.68</v>
+      </c>
+      <c r="D12">
+        <v>66</v>
+      </c>
+      <c r="E12">
+        <v>3498</v>
+      </c>
+      <c r="F12">
+        <v>1.886792</v>
+      </c>
+      <c r="G12">
+        <v>139.988565</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>23.7369835</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
+        <v>120245821095400425</v>
+      </c>
+      <c r="B13" t="str">
         <v>Yeni Gelenler - Carousel - Test</v>
       </c>
-      <c r="B13" t="str">
-        <v>1710.06</v>
-      </c>
-      <c r="C13" t="str">
-        <v>483</v>
-      </c>
-      <c r="D13" t="str">
-        <v>2.589396</v>
-      </c>
-      <c r="E13" t="str">
-        <v>91.677478</v>
-      </c>
-      <c r="F13" t="str">
-        <v>2026-05-11</v>
-      </c>
-      <c r="G13" t="str">
-        <v>2026-05-17</v>
+      <c r="C13">
+        <v>1737.1</v>
+      </c>
+      <c r="D13">
+        <v>531</v>
+      </c>
+      <c r="E13">
+        <v>19848</v>
+      </c>
+      <c r="F13">
+        <v>2.675333</v>
+      </c>
+      <c r="G13">
+        <v>87.520153</v>
+      </c>
+      <c r="H13">
+        <v>12.070693</v>
+      </c>
+      <c r="I13">
+        <v>648.2892947</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
+        <v>120245821111900425</v>
+      </c>
+      <c r="B14" t="str">
         <v>Bayram - Carousel - Test</v>
       </c>
-      <c r="B14" t="str">
-        <v>748.48</v>
-      </c>
-      <c r="C14" t="str">
-        <v>87</v>
-      </c>
-      <c r="D14" t="str">
-        <v>1.645234</v>
-      </c>
-      <c r="E14" t="str">
-        <v>141.543116</v>
-      </c>
-      <c r="F14" t="str">
-        <v>2026-05-11</v>
-      </c>
-      <c r="G14" t="str">
-        <v>2026-05-17</v>
+      <c r="C14">
+        <v>510.17</v>
+      </c>
+      <c r="D14">
+        <v>62</v>
+      </c>
+      <c r="E14">
+        <v>3522</v>
+      </c>
+      <c r="F14">
+        <v>1.760363</v>
+      </c>
+      <c r="G14">
+        <v>144.852357</v>
+      </c>
+      <c r="H14">
+        <v>2.29349</v>
+      </c>
+      <c r="I14">
+        <v>135.39652429999998</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
+        <v>120245821121640425</v>
+      </c>
+      <c r="B15" t="str">
         <v>Tişört Kategorisi - Carousel - Test</v>
       </c>
-      <c r="B15" t="str">
-        <v>766.36</v>
-      </c>
-      <c r="C15" t="str">
-        <v>95</v>
-      </c>
-      <c r="D15" t="str">
-        <v>1.455493</v>
-      </c>
-      <c r="E15" t="str">
-        <v>117.41382</v>
-      </c>
-      <c r="F15" t="str">
-        <v>2026-05-11</v>
-      </c>
-      <c r="G15" t="str">
-        <v>2026-05-17</v>
+      <c r="C15">
+        <v>505.45</v>
+      </c>
+      <c r="D15">
+        <v>66</v>
+      </c>
+      <c r="E15">
+        <v>4062</v>
+      </c>
+      <c r="F15">
+        <v>1.624815</v>
+      </c>
+      <c r="G15">
+        <v>124.433776</v>
+      </c>
+      <c r="H15">
+        <v>4.688891</v>
+      </c>
+      <c r="I15">
+        <v>254.49747240000002</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
+        <v>120246025828100425</v>
+      </c>
+      <c r="B16" t="str">
         <v>Reels - Takım - Test - Scale</v>
       </c>
-      <c r="B16" t="str">
-        <v>2383.94</v>
-      </c>
-      <c r="C16" t="str">
-        <v>499</v>
-      </c>
-      <c r="D16" t="str">
-        <v>2.093121</v>
-      </c>
-      <c r="E16" t="str">
-        <v>99.997483</v>
-      </c>
-      <c r="F16" t="str">
-        <v>2026-05-11</v>
-      </c>
-      <c r="G16" t="str">
-        <v>2026-05-17</v>
+      <c r="C16">
+        <v>2976.51</v>
+      </c>
+      <c r="D16">
+        <v>639</v>
+      </c>
+      <c r="E16">
+        <v>29426</v>
+      </c>
+      <c r="F16">
+        <v>2.171549</v>
+      </c>
+      <c r="G16">
+        <v>101.152382</v>
+      </c>
+      <c r="H16">
+        <v>8.990862</v>
+      </c>
+      <c r="I16">
+        <v>482.85884179999994</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G16"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I16"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I6"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>campaignId</v>
+      </c>
+      <c r="B1" t="str">
+        <v>campaignName</v>
+      </c>
+      <c r="C1" t="str">
+        <v>spend</v>
+      </c>
+      <c r="D1" t="str">
+        <v>clicks</v>
+      </c>
+      <c r="E1" t="str">
+        <v>impressions</v>
+      </c>
+      <c r="F1" t="str">
+        <v>ctr</v>
+      </c>
+      <c r="G1" t="str">
+        <v>cpm</v>
+      </c>
+      <c r="H1" t="str">
+        <v>roas</v>
+      </c>
+      <c r="I1" t="str">
+        <v>score</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>120245821095400425</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Yeni Gelenler - Carousel - Test</v>
+      </c>
+      <c r="C2">
+        <v>1737.1</v>
+      </c>
+      <c r="D2">
+        <v>531</v>
+      </c>
+      <c r="E2">
+        <v>19848</v>
+      </c>
+      <c r="F2">
+        <v>2.675333</v>
+      </c>
+      <c r="G2">
+        <v>87.520153</v>
+      </c>
+      <c r="H2">
+        <v>12.070693</v>
+      </c>
+      <c r="I2">
+        <v>648.2892947</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>120246025828100425</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Reels - Takım - Test - Scale</v>
+      </c>
+      <c r="C3">
+        <v>2976.51</v>
+      </c>
+      <c r="D3">
+        <v>639</v>
+      </c>
+      <c r="E3">
+        <v>29426</v>
+      </c>
+      <c r="F3">
+        <v>2.171549</v>
+      </c>
+      <c r="G3">
+        <v>101.152382</v>
+      </c>
+      <c r="H3">
+        <v>8.990862</v>
+      </c>
+      <c r="I3">
+        <v>482.85884179999994</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>120229177507470425</v>
+      </c>
+      <c r="B4" t="str">
+        <v>FB/RT/Dynamic</v>
+      </c>
+      <c r="C4">
+        <v>4846.68</v>
+      </c>
+      <c r="D4">
+        <v>877</v>
+      </c>
+      <c r="E4">
+        <v>38990</v>
+      </c>
+      <c r="F4">
+        <v>2.249295</v>
+      </c>
+      <c r="G4">
+        <v>124.305719</v>
+      </c>
+      <c r="H4">
+        <v>8.248112</v>
+      </c>
+      <c r="I4">
+        <v>444.96092810000005</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>120245821039980425</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Reels - Takım - Test</v>
+      </c>
+      <c r="C5">
+        <v>1685</v>
+      </c>
+      <c r="D5">
+        <v>455</v>
+      </c>
+      <c r="E5">
+        <v>16933</v>
+      </c>
+      <c r="F5">
+        <v>2.687061</v>
+      </c>
+      <c r="G5">
+        <v>99.509833</v>
+      </c>
+      <c r="H5">
+        <v>7.64505</v>
+      </c>
+      <c r="I5">
+        <v>426.0427367</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>120214021839830425</v>
+      </c>
+      <c r="B6" t="str">
+        <v>FB/RT/İçerik</v>
+      </c>
+      <c r="C6">
+        <v>13348.16</v>
+      </c>
+      <c r="D6">
+        <v>2354</v>
+      </c>
+      <c r="E6">
+        <v>112476</v>
+      </c>
+      <c r="F6">
+        <v>2.092891</v>
+      </c>
+      <c r="G6">
+        <v>118.675629</v>
+      </c>
+      <c r="H6">
+        <v>5.55955</v>
+      </c>
+      <c r="I6">
+        <v>307.9677571</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:I6"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I6"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>campaignId</v>
+      </c>
+      <c r="B1" t="str">
+        <v>campaignName</v>
+      </c>
+      <c r="C1" t="str">
+        <v>spend</v>
+      </c>
+      <c r="D1" t="str">
+        <v>clicks</v>
+      </c>
+      <c r="E1" t="str">
+        <v>impressions</v>
+      </c>
+      <c r="F1" t="str">
+        <v>ctr</v>
+      </c>
+      <c r="G1" t="str">
+        <v>cpm</v>
+      </c>
+      <c r="H1" t="str">
+        <v>roas</v>
+      </c>
+      <c r="I1" t="str">
+        <v>score</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>120245821072940425</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Çok Satanlar Kategorisi - Carousel - Test</v>
+      </c>
+      <c r="C2">
+        <v>489.68</v>
+      </c>
+      <c r="D2">
+        <v>66</v>
+      </c>
+      <c r="E2">
+        <v>3498</v>
+      </c>
+      <c r="F2">
+        <v>1.886792</v>
+      </c>
+      <c r="G2">
+        <v>139.988565</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>23.7369835</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>120245818053700425</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Reels - Bayram İndirimi  - Test</v>
+      </c>
+      <c r="C3">
+        <v>475.9</v>
+      </c>
+      <c r="D3">
+        <v>74</v>
+      </c>
+      <c r="E3">
+        <v>3890</v>
+      </c>
+      <c r="F3">
+        <v>1.902314</v>
+      </c>
+      <c r="G3">
+        <v>122.339332</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>25.8123468</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>120229338955800425</v>
+      </c>
+      <c r="B4" t="str">
+        <v>FB/RT/Crousel</v>
+      </c>
+      <c r="C4">
+        <v>2003.7</v>
+      </c>
+      <c r="D4">
+        <v>463</v>
+      </c>
+      <c r="E4">
+        <v>24075</v>
+      </c>
+      <c r="F4">
+        <v>1.923157</v>
+      </c>
+      <c r="G4">
+        <v>83.227414</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>30.140398600000005</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>120238452559310425</v>
+      </c>
+      <c r="B5" t="str">
+        <v>FB/RT/Traffik/Mağaza</v>
+      </c>
+      <c r="C5">
+        <v>1387.19</v>
+      </c>
+      <c r="D5">
+        <v>457</v>
+      </c>
+      <c r="E5">
+        <v>24613</v>
+      </c>
+      <c r="F5">
+        <v>1.856742</v>
+      </c>
+      <c r="G5">
+        <v>56.360054</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>31.498834599999995</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>120245580624510425</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Satışlar-DENEME SEVDE</v>
+      </c>
+      <c r="C6">
+        <v>1413.83</v>
+      </c>
+      <c r="D6">
+        <v>1841</v>
+      </c>
+      <c r="E6">
+        <v>46537</v>
+      </c>
+      <c r="F6">
+        <v>3.955992</v>
+      </c>
+      <c r="G6">
+        <v>30.380772</v>
+      </c>
+      <c r="H6">
+        <v>0.551693</v>
+      </c>
+      <c r="I6">
+        <v>103.6664128</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:I6"/>
   </ignoredErrors>
 </worksheet>
 </file>